--- a/manual_testing/SauceDemo_test_cases.xlsx
+++ b/manual_testing/SauceDemo_test_cases.xlsx
@@ -1,39 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandra\Documents\IT Bootcamp\Projekat\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E1150D-D860-4EAF-BE14-AD33E2BA311F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21540" windowHeight="15420" tabRatio="500" firstSheet="15" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TC_1_1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="TC_1_2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="TC_1_3" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="TC_1_4" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="TC_1_5" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="TC_1_6" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="TC_2_1" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="TC_2_2" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="TC_2_3" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="TC_3_1" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="TC_3_2" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="TC_4_1" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="TC_5_1" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="TC_5_2" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="TC_5_3" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="TC_5_4" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="TC_5_5" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="TC_5_6" sheetId="18" state="visible" r:id="rId20"/>
-    <sheet name="TC_6_2" sheetId="19" state="visible" r:id="rId21"/>
-    <sheet name="TC_6_3" sheetId="20" state="visible" r:id="rId22"/>
-    <sheet name="TC_6_4" sheetId="21" state="visible" r:id="rId23"/>
-    <sheet name="TC_6_5" sheetId="22" state="visible" r:id="rId24"/>
-    <sheet name="TC_6_6" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="TC_1_1" sheetId="1" r:id="rId1"/>
+    <sheet name="TC_1_2" sheetId="2" r:id="rId2"/>
+    <sheet name="TC_1_3" sheetId="3" r:id="rId3"/>
+    <sheet name="TC_1_4" sheetId="4" r:id="rId4"/>
+    <sheet name="TC_1_5" sheetId="5" r:id="rId5"/>
+    <sheet name="TC_1_6" sheetId="6" r:id="rId6"/>
+    <sheet name="TC_2_1" sheetId="7" r:id="rId7"/>
+    <sheet name="TC_2_2" sheetId="8" r:id="rId8"/>
+    <sheet name="TC_2_3" sheetId="9" r:id="rId9"/>
+    <sheet name="TC_3_1" sheetId="10" r:id="rId10"/>
+    <sheet name="TC_3_2" sheetId="11" r:id="rId11"/>
+    <sheet name="TC_4_1" sheetId="12" r:id="rId12"/>
+    <sheet name="TC_5_1" sheetId="13" r:id="rId13"/>
+    <sheet name="TC_5_2" sheetId="14" r:id="rId14"/>
+    <sheet name="TC_5_3" sheetId="15" r:id="rId15"/>
+    <sheet name="TC_5_4" sheetId="16" r:id="rId16"/>
+    <sheet name="TC_5_5" sheetId="17" r:id="rId17"/>
+    <sheet name="TC_5_6" sheetId="18" r:id="rId18"/>
+    <sheet name="TC_6_2" sheetId="19" r:id="rId19"/>
+    <sheet name="TC_6_3" sheetId="20" r:id="rId20"/>
+    <sheet name="TC_6_4" sheetId="21" r:id="rId21"/>
+    <sheet name="TC_6_5" sheetId="22" r:id="rId22"/>
+    <sheet name="TC_6_6" sheetId="23" r:id="rId23"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -44,61 +52,61 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="154">
   <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test case name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can log in with valid credentials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clear the Username field and enter valid username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard_user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"standard_user" is in Username text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clear the Password field and enter valid password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">secret_sauce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"secret_sauce" is in Password text field protected with dots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on Login button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login is successfule and user is on Saucedemo inventory page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is on Saucedemo login page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can not log in with invalid username</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>TC_1</t>
+  </si>
+  <si>
+    <t>Test case name</t>
+  </si>
+  <si>
+    <t>Verify that user can log in with valid credentials</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Expected result</t>
+  </si>
+  <si>
+    <t>Clear the Username field and enter valid username</t>
+  </si>
+  <si>
+    <t>standard_user</t>
+  </si>
+  <si>
+    <t>"standard_user" is in Username text field</t>
+  </si>
+  <si>
+    <t>Clear the Password field and enter valid password</t>
+  </si>
+  <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>"secret_sauce" is in Password text field protected with dots</t>
+  </si>
+  <si>
+    <t>Click on Login button</t>
+  </si>
+  <si>
+    <t>Login is successfule and user is on Saucedemo inventory page</t>
+  </si>
+  <si>
+    <t>Conditions</t>
+  </si>
+  <si>
+    <t>User is on Saucedemo login page</t>
+  </si>
+  <si>
+    <t>TC_2</t>
+  </si>
+  <si>
+    <t>Verify that user can not log in with invalid username</t>
   </si>
   <si>
     <r>
@@ -108,7 +116,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Clear the Username field and enter</t>
+      <t>Clear the Username field and enter</t>
     </r>
     <r>
       <rPr>
@@ -121,19 +129,19 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">strange_user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"strange_user" is in Username text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User can not login and is still on Saucedemo login page, proper error message is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can not log in with invalid password</t>
+    <t>strange_user</t>
+  </si>
+  <si>
+    <t>"strange_user" is in Username text field</t>
+  </si>
+  <si>
+    <t>User can not login and is still on Saucedemo login page, proper error message is displayed</t>
+  </si>
+  <si>
+    <t>TC_3</t>
+  </si>
+  <si>
+    <t>Verify that user can not log in with invalid password</t>
   </si>
   <si>
     <r>
@@ -143,7 +151,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Clear the Username field and enter</t>
+      <t>Clear the Username field and enter</t>
     </r>
     <r>
       <rPr>
@@ -156,259 +164,244 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Clear the Password field and enter invalid password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wrong_sauce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"wrong_sauce" is in Password text field protected with dots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can not log in with empty Username field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clear the Username field and leave it empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username field is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User can not login, proper error message that username is required is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_1_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can not log in with empty Password field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clear the Username field and enter valid Username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"standard_user" is in Username field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clear the Password field and leave it empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Password field is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User can not login and is still on Saucedemo login page, proper error message that password is required is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_1_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can not log in with empty Username and Password field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is still on Saucedemo login page, proper error message is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_2_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can add an item to Cart from Inventory page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on "Add to cart" button in first item field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Button border line is red, text is changed to "Remove item", number 1 is displayed on Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart page is open, there is an added product with Quantity 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in as “standard_user” and  is on Saucedemo Inventory page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_2_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can remove added item from Cart from Inventory page</t>
+    <t>Clear the Password field and enter invalid password</t>
+  </si>
+  <si>
+    <t>wrong_sauce</t>
+  </si>
+  <si>
+    <t>"wrong_sauce" is in Password text field protected with dots</t>
+  </si>
+  <si>
+    <t>TC_4</t>
+  </si>
+  <si>
+    <t>Verify that user can not log in with empty Username field</t>
+  </si>
+  <si>
+    <t>Clear the Username field and leave it empty</t>
+  </si>
+  <si>
+    <t>Username field is empty</t>
+  </si>
+  <si>
+    <t>User can not login, proper error message that username is required is displayed</t>
+  </si>
+  <si>
+    <t>TC_1_5</t>
+  </si>
+  <si>
+    <t>Verify that user can not log in with empty Password field</t>
+  </si>
+  <si>
+    <t>Clear the Username field and enter valid Username</t>
+  </si>
+  <si>
+    <t>"standard_user" is in Username field</t>
+  </si>
+  <si>
+    <t>Clear the Password field and leave it empty</t>
+  </si>
+  <si>
+    <t>Password field is empty</t>
+  </si>
+  <si>
+    <t>User can not login and is still on Saucedemo login page, proper error message that password is required is displayed</t>
+  </si>
+  <si>
+    <t>TC_1_6</t>
+  </si>
+  <si>
+    <t>Verify that user can not log in with empty Username and Password field</t>
+  </si>
+  <si>
+    <t>User is still on Saucedemo login page, proper error message is displayed</t>
+  </si>
+  <si>
+    <t>TC_2_1</t>
+  </si>
+  <si>
+    <t>Verify that user can add an item to Cart from Inventory page</t>
+  </si>
+  <si>
+    <t>Click on "Add to cart" button in first item field</t>
+  </si>
+  <si>
+    <t>Button border line is red, text is changed to "Remove item", number 1 is displayed on Cart icon</t>
+  </si>
+  <si>
+    <t>Click on Cart icon</t>
+  </si>
+  <si>
+    <t>Cart page is open, there is an added product with Quantity 1</t>
+  </si>
+  <si>
+    <t>User is logged in as “standard_user” and  is on Saucedemo Inventory page</t>
+  </si>
+  <si>
+    <t>TC_2_2</t>
+  </si>
+  <si>
+    <t>Verify that user can remove added item from Cart from Inventory page</t>
   </si>
   <si>
     <t xml:space="preserve">Click on "Add to cart" button in first item field </t>
   </si>
   <si>
-    <t xml:space="preserve">Click on "Remove" button in first item field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Button border line is black, text is changed to "Add to Cart", there is no number displayed on Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart page is open, there are no items in it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_2_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can add 3 item to Cart from Inventory page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on "Add to cart" button in second item field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Button border line is red, text is changed to "Remove item", number 2 is displayed on Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on "Add to cart" button in third item field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Button border line is red, text is changed to "Remove item", number 3 is displayed on Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart page is open, there are 3  added product each Quantity of 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_3_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can add an item to Cart from single Item page</t>
+    <t>Click on "Remove" button in first item field</t>
+  </si>
+  <si>
+    <t>Button border line is black, text is changed to "Add to Cart", there is no number displayed on Cart icon</t>
+  </si>
+  <si>
+    <t>Cart page is open, there are no items in it</t>
+  </si>
+  <si>
+    <t>TC_2_3</t>
+  </si>
+  <si>
+    <t>Verify that user can add 3 item to Cart from Inventory page</t>
+  </si>
+  <si>
+    <t>Click on "Add to cart" button in second item field</t>
+  </si>
+  <si>
+    <t>Button border line is red, text is changed to "Remove item", number 2 is displayed on Cart icon</t>
+  </si>
+  <si>
+    <t>Click on "Add to cart" button in third item field</t>
+  </si>
+  <si>
+    <t>Button border line is red, text is changed to "Remove item", number 3 is displayed on Cart icon</t>
+  </si>
+  <si>
+    <t>Cart page is open, there are 3  added product each Quantity of 1</t>
+  </si>
+  <si>
+    <t>TC_3_1</t>
+  </si>
+  <si>
+    <t>Verify that user can add an item to Cart from single Item page</t>
   </si>
   <si>
     <t xml:space="preserve">Click on "Add to cart" button </t>
   </si>
   <si>
-    <t xml:space="preserve">User is logged in as “standard_user” and is on single Item page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_3_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can remove an item from Cart from single Item page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_4_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can Log out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on burger manu icom</t>
+    <t>User is logged in as “standard_user” and is on single Item page</t>
+  </si>
+  <si>
+    <t>TC_3_2</t>
+  </si>
+  <si>
+    <t>Verify that user can remove an item from Cart from single Item page</t>
+  </si>
+  <si>
+    <t>TC_4_1</t>
+  </si>
+  <si>
+    <t>Click on burger manu icom</t>
   </si>
   <si>
     <t xml:space="preserve">Dropdown navigation menu is shown </t>
   </si>
   <si>
-    <t xml:space="preserve">Click on "Logout" option from dropdown navigationmenu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is loggedout and on login page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_5_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can add quantity to items in Cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on Quantity field and input a number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"3"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cursor is in Quantity field and user can input a number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in as “standard_user” and is on Cart page containing 1 item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_5_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can not input negative quantity to items in Cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"-2"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cursor is in Quantity field and user can not input a negative number, Error message is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_5_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can remove items from Cart from Cart page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click Remove Button for the firs item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There are two items left in the Cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click Remove Button for the second item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There is one item left in the Cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click Remove Button for the third item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There are no items left in the Cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in as “standard_user” and is on Cart page containing 3 item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_5_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can not proceed to Checkout with emptyCart from Cart page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on the Continue button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Continue button can not be clicked. Error message is shown indicating that a Cart can not be empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in as “standard_user” and there are no items in the Cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_5_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that user can proceed to Checkout and finish payment with items in Cart page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on the Checkout button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is on Checkout-step-one page</t>
+    <t>Click on "Logout" option from dropdown navigationmenu</t>
+  </si>
+  <si>
+    <t>User is loggedout and on login page</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <t>TC_5_1</t>
+  </si>
+  <si>
+    <t>Click on Quantity field and input a number</t>
+  </si>
+  <si>
+    <t>"3"</t>
+  </si>
+  <si>
+    <t>Cursor is in Quantity field and user can input a number</t>
+  </si>
+  <si>
+    <t>User is logged in as “standard_user” and is on Cart page containing 1 item</t>
+  </si>
+  <si>
+    <t>TC_5_2</t>
+  </si>
+  <si>
+    <t>Verify that user can not input negative quantity to items in Cart</t>
+  </si>
+  <si>
+    <t>"-2"</t>
+  </si>
+  <si>
+    <t>Cursor is in Quantity field and user can not input a negative number, Error message is displayed</t>
+  </si>
+  <si>
+    <t>TC_5_3</t>
+  </si>
+  <si>
+    <t>Verify that user can remove items from Cart from Cart page</t>
+  </si>
+  <si>
+    <t>Click Remove Button for the firs item</t>
+  </si>
+  <si>
+    <t>There are two items left in the Cart</t>
+  </si>
+  <si>
+    <t>Click Remove Button for the second item</t>
+  </si>
+  <si>
+    <t>There is one item left in the Cart</t>
+  </si>
+  <si>
+    <t>Click Remove Button for the third item</t>
+  </si>
+  <si>
+    <t>There are no items left in the Cart</t>
+  </si>
+  <si>
+    <t>User is logged in as “standard_user” and is on Cart page containing 3 item</t>
+  </si>
+  <si>
+    <t>TC_5_4</t>
+  </si>
+  <si>
+    <t>Click on the Continue button</t>
+  </si>
+  <si>
+    <t>User is logged in as “standard_user” and there are no items in the Cart</t>
+  </si>
+  <si>
+    <t>TC_5_5</t>
+  </si>
+  <si>
+    <t>Click on the Checkout button</t>
+  </si>
+  <si>
+    <t>User is on Checkout-step-one page</t>
   </si>
   <si>
     <t xml:space="preserve">Clear the First name field and enter valid first name </t>
   </si>
   <si>
-    <t xml:space="preserve">"Alex"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Alex" is in First name text field</t>
+    <t>"Alex"</t>
+  </si>
+  <si>
+    <t>"Alex" is in First name text field</t>
   </si>
   <si>
     <t xml:space="preserve">Clear the Last name field and enter valid last name </t>
   </si>
   <si>
-    <t xml:space="preserve">"Linch"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Linch" is in Last name text field</t>
+    <t>"Linch"</t>
+  </si>
+  <si>
+    <t>"Linch" is in Last name text field</t>
   </si>
   <si>
     <r>
@@ -418,7 +411,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Clear the Zip/Postal code text field and enter valid</t>
+      <t>Clear the Zip/Postal code text field and enter valid</t>
     </r>
     <r>
       <rPr>
@@ -431,106 +424,103 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">"11000"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"11000" is in Zip/Postal code text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is on Checkout-step-two page, items from the cart are listed with correct quantity and price, total price is correct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on the Finish button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is on Checkout-complete page, Success message is shown, there are no numbers on Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in as “standard_user” and is on Cart page containing 3 items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_5_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that Cart is empty after payment was completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input valid first name in First name text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asure Last name text field is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last name text field is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delete all from Zip/Postal code field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zip/Postal code text field is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is on Checkout-step-two page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is on Checkout-complete page,  there are no numbers on Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click  Back Home button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is on Inventory page,  there are no numbers on Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click Cart icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There are no items in Cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_6_2</t>
+    <t>"11000"</t>
+  </si>
+  <si>
+    <t>"11000" is in Zip/Postal code text field</t>
+  </si>
+  <si>
+    <t>User is on Checkout-step-two page, items from the cart are listed with correct quantity and price, total price is correct</t>
+  </si>
+  <si>
+    <t>Click on the Finish button</t>
+  </si>
+  <si>
+    <t>User is on Checkout-complete page, Success message is shown, there are no numbers on Cart icon</t>
+  </si>
+  <si>
+    <t>User is logged in as “standard_user” and is on Cart page containing 3 items</t>
+  </si>
+  <si>
+    <t>TC_5_6</t>
+  </si>
+  <si>
+    <t>Verify that Cart is empty after payment was completed</t>
+  </si>
+  <si>
+    <t>Input valid first name in First name text field</t>
+  </si>
+  <si>
+    <t>Asure Last name text field is empty</t>
+  </si>
+  <si>
+    <t>Last name text field is empty</t>
+  </si>
+  <si>
+    <t>Delete all from Zip/Postal code field</t>
+  </si>
+  <si>
+    <t>Zip/Postal code text field is empty</t>
+  </si>
+  <si>
+    <t>User is on Checkout-step-two page</t>
+  </si>
+  <si>
+    <t>User is on Checkout-complete page,  there are no numbers on Cart icon</t>
+  </si>
+  <si>
+    <t>Click  Back Home button</t>
+  </si>
+  <si>
+    <t>User is on Inventory page,  there are no numbers on Cart icon</t>
+  </si>
+  <si>
+    <t>Click Cart icon</t>
+  </si>
+  <si>
+    <t>There are no items in Cart</t>
+  </si>
+  <si>
+    <t>TC_6_2</t>
   </si>
   <si>
     <t xml:space="preserve">Verify that user can not continue to paying with numbers in First name field of  information form </t>
   </si>
   <si>
-    <t xml:space="preserve">Input numbers in First name text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"1234"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"1234" is in First name text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input valid last name in Last name text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input valid Zip/Postal code in Zip/Postal code text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User can not continue to paying, proper Error message is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in as standard_user and is on Checkout-step-one page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_6_3</t>
+    <t>Input numbers in First name text field</t>
+  </si>
+  <si>
+    <t>"1234"</t>
+  </si>
+  <si>
+    <t>"1234" is in First name text field</t>
+  </si>
+  <si>
+    <t>Input valid last name in Last name text field</t>
+  </si>
+  <si>
+    <t>Input valid Zip/Postal code in Zip/Postal code text field</t>
+  </si>
+  <si>
+    <t>User can not continue to paying, proper Error message is displayed</t>
+  </si>
+  <si>
+    <t>TC_6_3</t>
   </si>
   <si>
     <t xml:space="preserve">Verify that user can not continue to paying with numbers in Last name field of  information form </t>
   </si>
   <si>
-    <t xml:space="preserve">Input numbers in Last name text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"4321"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"4321" is in Last name text field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_6_4</t>
+    <t>Input numbers in Last name text field</t>
+  </si>
+  <si>
+    <t>"4321"</t>
+  </si>
+  <si>
+    <t>"4321" is in Last name text field</t>
+  </si>
+  <si>
+    <t>TC_6_4</t>
   </si>
   <si>
     <t xml:space="preserve">Verify that user can not continue to paying with empty First name field of  information form </t>
@@ -539,10 +529,10 @@
     <t xml:space="preserve">Delete all fromFirst name text field </t>
   </si>
   <si>
-    <t xml:space="preserve">First name text field is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_6_5</t>
+    <t>First name text field is empty</t>
+  </si>
+  <si>
+    <t>TC_6_5</t>
   </si>
   <si>
     <t xml:space="preserve">Verify that user can not continue to paying with empty Last name field of  information form </t>
@@ -551,20 +541,35 @@
     <t xml:space="preserve">Delete all from Last name text field </t>
   </si>
   <si>
-    <t xml:space="preserve">TC_6_6</t>
+    <t>TC_6_6</t>
   </si>
   <si>
     <t xml:space="preserve">Verify that user can not continue to paying with empty Zip/Postal code field of  information form </t>
+  </si>
+  <si>
+    <t>Verify that user can increase quantity of an item in Cart</t>
+  </si>
+  <si>
+    <t>Verify that user can proceed to Checkout and complete the purchase with items in Cart</t>
+  </si>
+  <si>
+    <t>Verify that user can log out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that user can not proceed to Checkout with empty Cart </t>
+  </si>
+  <si>
+    <t>Checkout button can not be clicked. Error message is shown indicating that a Cart can not be empty</t>
+  </si>
+  <si>
+    <t>User is logged in as standard_user and on Cart page containing one item</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,22 +577,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -609,7 +599,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999"/>
+        <fgColor theme="7" tint="0.79989013336588644"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -621,108 +611,62 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment textRotation="255"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="255" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -781,13 +725,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -829,14 +789,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -889,23 +849,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -914,7 +873,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -923,7 +882,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -934,7 +893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -945,7 +904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -956,7 +915,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -965,95 +924,87 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1013,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1071,7 +1022,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1082,7 +1033,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>66</v>
       </c>
@@ -1091,7 +1042,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
@@ -1100,100 +1051,92 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1202,7 +1145,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1211,7 +1154,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1222,7 +1165,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>53</v>
       </c>
@@ -1231,7 +1174,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>54</v>
       </c>
@@ -1240,7 +1183,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
@@ -1249,95 +1192,87 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,16 +1281,16 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1366,136 +1301,128 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1506,147 +1433,129 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1657,147 +1566,129 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1808,153 +1699,135 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1965,145 +1838,127 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2114,171 +1969,153 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2289,177 +2126,159 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C6" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="12"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2470,136 +2289,128 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C6" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2608,7 +2419,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2617,7 +2428,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2628,7 +2439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>19</v>
       </c>
@@ -2639,7 +2450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -2650,7 +2461,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -2659,113 +2470,105 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2776,154 +2579,146 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2934,152 +2729,144 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3090,152 +2877,144 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3246,134 +3025,126 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C6" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3382,7 +3153,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3391,7 +3162,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3402,7 +3173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
@@ -3413,7 +3184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>26</v>
       </c>
@@ -3424,7 +3195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3433,95 +3204,87 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3530,7 +3293,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3539,7 +3302,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3550,7 +3313,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
@@ -3559,7 +3322,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -3570,7 +3333,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3579,95 +3342,87 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3676,7 +3431,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3685,7 +3440,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3696,7 +3451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
@@ -3707,7 +3462,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
@@ -3716,7 +3471,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3725,95 +3480,87 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3822,16 +3569,16 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3842,7 +3589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
@@ -3851,7 +3598,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
@@ -3860,7 +3607,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3869,95 +3616,87 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3966,7 +3705,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3975,7 +3714,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3986,7 +3725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>46</v>
       </c>
@@ -3995,7 +3734,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
@@ -4004,100 +3743,92 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4106,7 +3837,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -4115,7 +3846,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -4126,7 +3857,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>53</v>
       </c>
@@ -4135,7 +3866,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>54</v>
       </c>
@@ -4144,7 +3875,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
@@ -4153,94 +3884,86 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.29"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4249,7 +3972,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -4258,7 +3981,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -4269,7 +3992,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>46</v>
       </c>
@@ -4278,7 +4001,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>59</v>
       </c>
@@ -4287,7 +4010,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>61</v>
       </c>
@@ -4296,7 +4019,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -4305,71 +4028,66 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>